--- a/Excel/Datas/item.xlsx
+++ b/Excel/Datas/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12920"/>
+    <workbookView windowHeight="12920"/>
   </bookViews>
   <sheets>
     <sheet name="item_table" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>##var</t>
   </si>
@@ -35,7 +35,10 @@
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
+    <t>type</t>
+  </si>
+  <si>
+    <t>desc</t>
   </si>
   <si>
     <t>##type</t>
@@ -47,6 +50,9 @@
     <t>ItemTypeEnum</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -56,7 +62,10 @@
     <t>ID</t>
   </si>
   <si>
-    <t>名字(不填从id解析)</t>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>描述</t>
   </si>
   <si>
     <t>回血0</t>
@@ -1185,7 +1194,9 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -1223,15 +1234,17 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
-      <c r="D3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -1248,7 +1261,7 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1267,17 +1280,19 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" ht="17.55" spans="1:17">
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E5" s="2"/>
       <c r="F5" s="6"/>
       <c r="G5" s="7"/>
@@ -1294,10 +1309,10 @@
     </row>
     <row r="6" ht="17.55" spans="2:17">
       <c r="B6" s="3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -1332,7 +1347,7 @@
       <c r="P7" s="18"/>
       <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="2:17">
+    <row r="8" ht="17.55" spans="2:17">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -1350,7 +1365,7 @@
       <c r="P8" s="18"/>
       <c r="Q8" s="4"/>
     </row>
-    <row r="9" spans="2:17">
+    <row r="9" ht="17.55" spans="2:17">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -1368,7 +1383,7 @@
       <c r="P9" s="18"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="2:17">
+    <row r="10" ht="17.55" spans="2:17">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -1386,7 +1401,7 @@
       <c r="P10" s="18"/>
       <c r="Q10" s="4"/>
     </row>
-    <row r="11" spans="2:17">
+    <row r="11" ht="17.55" spans="2:17">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -1404,7 +1419,7 @@
       <c r="P11" s="18"/>
       <c r="Q11" s="4"/>
     </row>
-    <row r="12" spans="2:17">
+    <row r="12" ht="17.55" spans="2:17">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -1422,7 +1437,7 @@
       <c r="P12" s="18"/>
       <c r="Q12" s="4"/>
     </row>
-    <row r="13" spans="2:17">
+    <row r="13" ht="17.55" spans="2:17">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -1440,7 +1455,7 @@
       <c r="P13" s="18"/>
       <c r="Q13" s="4"/>
     </row>
-    <row r="14" spans="2:17">
+    <row r="14" ht="17.55" spans="2:17">
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -1458,7 +1473,7 @@
       <c r="P14" s="18"/>
       <c r="Q14" s="4"/>
     </row>
-    <row r="15" spans="2:17">
+    <row r="15" ht="17.55" spans="2:17">
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -1476,7 +1491,7 @@
       <c r="P15" s="18"/>
       <c r="Q15" s="4"/>
     </row>
-    <row r="16" spans="2:17">
+    <row r="16" ht="17.55" spans="2:17">
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -1494,7 +1509,7 @@
       <c r="P16" s="18"/>
       <c r="Q16" s="4"/>
     </row>
-    <row r="17" spans="2:17">
+    <row r="17" ht="17.55" spans="2:17">
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>

--- a/Excel/Datas/item.xlsx
+++ b/Excel/Datas/item.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="12920"/>
+    <workbookView windowWidth="28000" windowHeight="12920"/>
   </bookViews>
   <sheets>
     <sheet name="item_table" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
     <t>回血0</t>
   </si>
   <si>
-    <t>道具卡</t>
+    <t>卡牌</t>
   </si>
 </sst>
 </file>
@@ -1280,7 +1280,7 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" ht="17.55" spans="1:17">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -1307,7 +1307,7 @@
       <c r="P5" s="16"/>
       <c r="Q5" s="3"/>
     </row>
-    <row r="6" ht="17.55" spans="2:17">
+    <row r="6" spans="2:17">
       <c r="B6" s="3" t="s">
         <v>13</v>
       </c>

--- a/Excel/Datas/item.xlsx
+++ b/Excel/Datas/item.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>##var</t>
   </si>
@@ -41,6 +41,9 @@
     <t>desc</t>
   </si>
   <si>
+    <t>max_stack</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -53,6 +56,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>ushort</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -66,6 +72,9 @@
   </si>
   <si>
     <t>描述</t>
+  </si>
+  <si>
+    <t>最大堆叠数量</t>
   </si>
   <si>
     <t>回血0</t>
@@ -1197,7 +1206,9 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1"/>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -1234,18 +1245,20 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -1261,7 +1274,7 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1280,20 +1293,22 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" ht="17.55" spans="1:17">
+    <row r="5" spans="1:17">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="F5" s="6"/>
       <c r="G5" s="7"/>
       <c r="H5" s="8"/>
@@ -1307,12 +1322,12 @@
       <c r="P5" s="16"/>
       <c r="Q5" s="3"/>
     </row>
-    <row r="6" spans="2:17">
+    <row r="6" ht="17.55" spans="2:17">
       <c r="B6" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>

--- a/Excel/Datas/item.xlsx
+++ b/Excel/Datas/item.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -56,7 +56,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>ushort</t>
+    <t>short</t>
   </si>
   <si>
     <t>##group</t>
@@ -77,10 +77,37 @@
     <t>最大堆叠数量</t>
   </si>
   <si>
-    <t>回血0</t>
+    <t>大森林</t>
   </si>
   <si>
     <t>卡牌</t>
+  </si>
+  <si>
+    <t>矿山</t>
+  </si>
+  <si>
+    <t>墓园</t>
+  </si>
+  <si>
+    <t>战斗哨塔</t>
+  </si>
+  <si>
+    <t>废铁厂</t>
+  </si>
+  <si>
+    <t>高速升级</t>
+  </si>
+  <si>
+    <t>装甲升级</t>
+  </si>
+  <si>
+    <t>重组升级</t>
+  </si>
+  <si>
+    <t>能量饮料</t>
+  </si>
+  <si>
+    <t>脏拖把</t>
   </si>
 </sst>
 </file>
@@ -103,14 +130,14 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -260,7 +287,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -281,6 +308,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD9F5D6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -496,7 +535,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -516,6 +555,21 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -680,7 +734,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,168 +746,174 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1293,7 +1353,7 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" ht="17.55" spans="1:17">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -1309,247 +1369,265 @@
       <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="3"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="4"/>
     </row>
     <row r="6" ht="17.55" spans="2:17">
       <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="4"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="5"/>
     </row>
     <row r="7" ht="17.55" spans="2:17">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="18"/>
-      <c r="Q7" s="4"/>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="5"/>
     </row>
     <row r="8" ht="17.55" spans="2:17">
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="18"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="4"/>
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="5"/>
     </row>
     <row r="9" ht="17.55" spans="2:17">
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="4"/>
+      <c r="B9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="5"/>
     </row>
     <row r="10" ht="17.55" spans="2:17">
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="18"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="4"/>
+      <c r="B10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="5"/>
     </row>
     <row r="11" ht="17.55" spans="2:17">
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="4"/>
+      <c r="B11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="5"/>
     </row>
     <row r="12" ht="17.55" spans="2:17">
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="18"/>
-      <c r="P12" s="18"/>
-      <c r="Q12" s="4"/>
+      <c r="B12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="5"/>
     </row>
     <row r="13" ht="17.55" spans="2:17">
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="4"/>
+      <c r="B13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="5"/>
     </row>
     <row r="14" ht="17.55" spans="2:17">
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="18"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="4"/>
+      <c r="B14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="19"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="5"/>
     </row>
     <row r="15" ht="17.55" spans="2:17">
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17"/>
-      <c r="O15" s="18"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="4"/>
+      <c r="B15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="5"/>
     </row>
     <row r="16" ht="17.55" spans="2:17">
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="18"/>
-      <c r="P16" s="18"/>
-      <c r="Q16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="5"/>
     </row>
     <row r="17" ht="17.55" spans="2:17">
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="5"/>
     </row>
     <row r="18" ht="17.55" spans="2:2">
-      <c r="B18" s="5"/>
+      <c r="B18" s="7"/>
     </row>
     <row r="19" ht="17.55" spans="2:2">
-      <c r="B19" s="5"/>
+      <c r="B19" s="7"/>
     </row>
     <row r="20" ht="17.55" spans="2:2">
-      <c r="B20" s="5"/>
+      <c r="B20" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/Datas/item.xlsx
+++ b/Excel/Datas/item.xlsx
@@ -1390,7 +1390,9 @@
         <v>17</v>
       </c>
       <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
       <c r="F6" s="11"/>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -1410,7 +1412,9 @@
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
       <c r="F7" s="7"/>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
@@ -1430,7 +1434,9 @@
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
       <c r="F8" s="7"/>
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
@@ -1450,7 +1456,9 @@
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
       <c r="F9" s="7"/>
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
@@ -1470,7 +1478,9 @@
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
       <c r="F10" s="7"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
@@ -1484,13 +1494,15 @@
       <c r="P10" s="20"/>
       <c r="Q10" s="5"/>
     </row>
-    <row r="11" ht="17.55" spans="2:17">
+    <row r="11" spans="2:17">
       <c r="B11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
+      <c r="E11" s="5">
+        <v>1</v>
+      </c>
       <c r="F11" s="7"/>
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
@@ -1510,7 +1522,9 @@
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
       <c r="F12" s="7"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
@@ -1530,7 +1544,9 @@
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
       <c r="F13" s="7"/>
       <c r="G13" s="12"/>
       <c r="H13" s="12"/>
@@ -1550,7 +1566,9 @@
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
+      <c r="E14" s="5">
+        <v>1</v>
+      </c>
       <c r="F14" s="7"/>
       <c r="G14" s="12"/>
       <c r="H14" s="12"/>
@@ -1570,7 +1588,9 @@
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
       <c r="F15" s="7"/>
       <c r="G15" s="12"/>
       <c r="H15" s="12"/>

--- a/Excel/Datas/item.xlsx
+++ b/Excel/Datas/item.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Project-SS\Excel\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77EE8BB5-3D77-42AB-B8B3-4F05D28D00B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="30240" windowHeight="12920"/>
   </bookViews>
   <sheets>
     <sheet name="item_table" sheetId="1" r:id="rId1"/>
@@ -24,6 +18,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -39,6 +35,9 @@
     <t>id</t>
   </si>
   <si>
+    <t>name</t>
+  </si>
+  <si>
     <t>type</t>
   </si>
   <si>
@@ -54,12 +53,12 @@
     <t>ItemEnum</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>ItemTypeEnum</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>short</t>
   </si>
   <si>
@@ -87,80 +86,77 @@
     <t>卡牌</t>
   </si>
   <si>
+    <t>放置在地图中。下一次获取怪兽时，必定会刷新一只野兽和一只植物。</t>
+  </si>
+  <si>
     <t>矿山</t>
   </si>
   <si>
+    <t>放置在地图中。立即获得5个水晶或生化物质。己方队伍每开始新的一圈冒险，都会获得1个水晶或生化物质。</t>
+  </si>
+  <si>
     <t>墓园</t>
   </si>
   <si>
+    <t>放置在地图中。下一次获取怪兽时，必定会刷新一只妖怪和一只昆虫。</t>
+  </si>
+  <si>
     <t>战斗哨塔</t>
   </si>
   <si>
+    <t>放置在地图中。在哨塔范围内，己方队伍的怪兽力量分别增加20%。若范围内存在精英敌人，则改为己方队伍的怪兽力量分别增加30%。</t>
+  </si>
+  <si>
     <t>废铁厂</t>
   </si>
   <si>
+    <t>放置在地图中。立即获取一张升级卡：高速升级，装甲升级或重组升级。下一次获取怪兽时，必定会刷新一只机械。</t>
+  </si>
+  <si>
     <t>高速升级</t>
   </si>
   <si>
+    <t>对目标己方怪兽使用。本次对战中，该怪兽的速度提高10点。如果该怪兽的种族是机械，则改为该怪兽的速度永久提高2点。</t>
+  </si>
+  <si>
     <t>装甲升级</t>
   </si>
   <si>
+    <t>对目标己方怪兽使用。本次对战中，该怪兽的力量和防御分别提高10点。如果该怪兽的种族是机械，则改为该怪兽的力量和防御分别永久提高1点。</t>
+  </si>
+  <si>
     <t>重组升级</t>
   </si>
   <si>
+    <t>对目标己方怪兽使用。本次对战中，该怪兽的恢复最大生命的50%。如果该怪兽的种族是机械，则改为该怪兽的最大生命永久提高5点。</t>
+  </si>
+  <si>
     <t>能量饮料</t>
   </si>
   <si>
+    <t>33能量饮料</t>
+  </si>
+  <si>
+    <t>对目标怪兽使用。如果目标是己方怪兽，则该怪兽接下来3次攻击会造成3倍伤害；如果目标是敌方怪兽，则该怪兽的力量降低80%。</t>
+  </si>
+  <si>
     <t>脏拖把</t>
   </si>
   <si>
-    <t>放置在地图中。下一次获取怪兽时，必定会刷新一只野兽和一只植物。</t>
-  </si>
-  <si>
-    <t>放置在地图中。立即获得5个水晶或生化物质。己方队伍每开始新的一圈冒险，都会获得1个水晶或生化物质。</t>
-  </si>
-  <si>
-    <t>放置在地图中。下一次获取怪兽时，必定会刷新一只妖怪和一只昆虫。</t>
-  </si>
-  <si>
-    <t>放置在地图中。在哨塔范围内，己方队伍的怪兽力量分别增加20%。若范围内存在精英敌人，则改为己方队伍的怪兽力量分别增加30%。</t>
-  </si>
-  <si>
-    <t>放置在地图中。立即获取一张升级卡：高速升级，装甲升级或重组升级。下一次获取怪兽时，必定会刷新一只机械。</t>
-  </si>
-  <si>
-    <t>对目标己方怪兽使用。本次对战中，该怪兽的速度提高10点。如果该怪兽的种族是机械，则改为该怪兽的速度永久提高2点。</t>
-  </si>
-  <si>
-    <t>对目标己方怪兽使用。本次对战中，该怪兽的力量和防御分别提高10点。如果该怪兽的种族是机械，则改为该怪兽的力量和防御分别永久提高1点。</t>
-  </si>
-  <si>
-    <t>对目标己方怪兽使用。本次对战中，该怪兽的恢复最大生命的50%。如果该怪兽的种族是机械，则改为该怪兽的最大生命永久提高5点。</t>
-  </si>
-  <si>
-    <t>对目标怪兽使用。如果目标是己方怪兽，则该怪兽接下来3次攻击会造成3倍伤害；如果目标是敌方怪兽，则该怪兽的力量降低80%。</t>
-  </si>
-  <si>
     <t>对目标敌方单位使用。该单位受到30点伤害（此伤害无视防御和适应）。</t>
-  </si>
-  <si>
-    <t>name</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>33能量饮料</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -169,6 +165,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
@@ -183,29 +186,158 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -214,25 +346,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79964598529007846"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39963988158818325"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.799645985290078"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399639881588183"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -244,6 +376,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFBBFBC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -268,12 +406,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -350,96 +668,382 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFF43308"/>
-      <color rgb="FFFF8680"/>
+      <color rgb="00F43308"/>
+      <color rgb="00FF8680"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -697,17 +1301,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:R20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="3" width="18.5" customWidth="1"/>
-    <col min="4" max="6" width="21.625" customWidth="1"/>
+    <col min="4" max="4" width="21.625" customWidth="1"/>
+    <col min="5" max="5" width="38.6964285714286" customWidth="1"/>
+    <col min="6" max="6" width="21.625" customWidth="1"/>
     <col min="7" max="7" width="13.5" customWidth="1"/>
     <col min="14" max="14" width="11.875" customWidth="1"/>
     <col min="15" max="15" width="9.625" customWidth="1"/>
@@ -715,24 +1321,24 @@
     <col min="18" max="18" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23" t="s">
-        <v>37</v>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -747,7 +1353,7 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -769,24 +1375,24 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>38</v>
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -801,9 +1407,9 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -823,380 +1429,380 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="5" ht="17.55" spans="1:18">
+      <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="4"/>
-    </row>
-    <row r="6" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="G5" s="12"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="21"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="5"/>
+    </row>
+    <row r="6" ht="17.55" spans="2:18">
+      <c r="B6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="C6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="8"/>
+    </row>
+    <row r="7" ht="17.55" spans="2:18">
+      <c r="B7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="8">
+        <v>1</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="8"/>
+    </row>
+    <row r="8" ht="17.55" spans="2:18">
+      <c r="B8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="8">
+        <v>1</v>
+      </c>
+      <c r="G8" s="9"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="8"/>
+    </row>
+    <row r="9" ht="17.55" spans="2:18">
+      <c r="B9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="8">
+        <v>1</v>
+      </c>
+      <c r="G9" s="9"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="8"/>
+    </row>
+    <row r="10" ht="17.55" spans="2:18">
+      <c r="B10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F10" s="8">
         <v>1</v>
       </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="5"/>
-    </row>
-    <row r="7" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
+      <c r="G10" s="9"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="8"/>
+    </row>
+    <row r="11" ht="17.55" spans="2:18">
+      <c r="B11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E11" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1</v>
+      </c>
+      <c r="G11" s="9"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="8"/>
+    </row>
+    <row r="12" ht="17.55" spans="2:18">
+      <c r="B12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="5">
+      <c r="E12" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="8">
         <v>1</v>
       </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="5"/>
-    </row>
-    <row r="8" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="G12" s="9"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="8"/>
+    </row>
+    <row r="13" ht="17.55" spans="2:18">
+      <c r="B13" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="8">
         <v>1</v>
       </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="5"/>
-    </row>
-    <row r="9" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="G13" s="9"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="8"/>
+    </row>
+    <row r="14" ht="17.55" spans="2:18">
+      <c r="B14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="8">
         <v>1</v>
       </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="5"/>
-    </row>
-    <row r="10" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="5">
+      <c r="G14" s="9"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="8"/>
+    </row>
+    <row r="15" ht="17.55" spans="2:18">
+      <c r="B15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="8">
         <v>1</v>
       </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="20"/>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="5"/>
-    </row>
-    <row r="11" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="5">
-        <v>1</v>
-      </c>
-      <c r="G11" s="7"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="20"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="5"/>
-    </row>
-    <row r="12" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="5">
-        <v>1</v>
-      </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="20"/>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="5"/>
-    </row>
-    <row r="13" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="5">
-        <v>1</v>
-      </c>
-      <c r="G13" s="7"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="20"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="5"/>
-    </row>
-    <row r="14" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="5">
-        <v>1</v>
-      </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="5"/>
-    </row>
-    <row r="15" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" s="5">
-        <v>1</v>
-      </c>
-      <c r="G15" s="7"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="5"/>
-    </row>
-    <row r="16" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="5"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="5"/>
-    </row>
-    <row r="17" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="5"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="20"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="5"/>
-    </row>
-    <row r="18" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="7"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="4"/>
-    </row>
-    <row r="19" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="7"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="2:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="7"/>
-      <c r="C20" s="22"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="8"/>
+    </row>
+    <row r="16" ht="17.55" spans="2:18">
+      <c r="B16" s="8"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="8"/>
+    </row>
+    <row r="17" ht="17.55" spans="2:18">
+      <c r="B17" s="8"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="8"/>
+    </row>
+    <row r="18" ht="17.55" spans="2:4">
+      <c r="B18" s="9"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" ht="17.55" spans="2:4">
+      <c r="B19" s="9"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" ht="17.55" spans="2:3">
+      <c r="B20" s="9"/>
+      <c r="C20" s="11"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Excel/Datas/item.xlsx
+++ b/Excel/Datas/item.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Project-SS\Excel\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC116DD2-3CCB-4E52-A0B9-808A25B83375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="12920"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="item_table" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -122,41 +126,36 @@
     <t>装甲升级</t>
   </si>
   <si>
+    <t>重组升级</t>
+  </si>
+  <si>
+    <t>对目标己方怪兽使用。本次对战中，该怪兽的恢复最大生命的50%。如果该怪兽的种族是机械，则改为该怪兽的最大生命永久提高5点。</t>
+  </si>
+  <si>
+    <t>能量饮料</t>
+  </si>
+  <si>
+    <t>33能量饮料</t>
+  </si>
+  <si>
+    <t>对目标怪兽使用。如果目标是己方怪兽，则该怪兽接下来3次攻击会造成3倍伤害；如果目标是敌方怪兽，则该怪兽的力量降低80%。</t>
+  </si>
+  <si>
+    <t>脏拖把</t>
+  </si>
+  <si>
+    <t>对目标敌方单位使用。该单位受到30点伤害（此伤害无视防御和适应）。</t>
+  </si>
+  <si>
     <t>对目标己方怪兽使用。本次对战中，该怪兽的力量和防御分别提高10点。如果该怪兽的种族是机械，则改为该怪兽的力量和防御分别永久提高1点。</t>
-  </si>
-  <si>
-    <t>重组升级</t>
-  </si>
-  <si>
-    <t>对目标己方怪兽使用。本次对战中，该怪兽的恢复最大生命的50%。如果该怪兽的种族是机械，则改为该怪兽的最大生命永久提高5点。</t>
-  </si>
-  <si>
-    <t>能量饮料</t>
-  </si>
-  <si>
-    <t>33能量饮料</t>
-  </si>
-  <si>
-    <t>对目标怪兽使用。如果目标是己方怪兽，则该怪兽接下来3次攻击会造成3倍伤害；如果目标是敌方怪兽，则该怪兽的力量降低80%。</t>
-  </si>
-  <si>
-    <t>脏拖把</t>
-  </si>
-  <si>
-    <t>对目标敌方单位使用。该单位受到30点伤害（此伤害无视防御和适应）。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,151 +192,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="43">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -346,25 +215,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799645985290078"/>
+        <fgColor theme="5" tint="0.79961546678060247"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399639881588183"/>
+        <fgColor theme="8" tint="0.39960936307870726"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79995117038483843"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,194 +273,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="14">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -668,253 +351,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -940,7 +381,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -982,68 +423,27 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="00F43308"/>
-      <color rgb="00FF8680"/>
+      <color rgb="FFF43308"/>
+      <color rgb="FFFF8680"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1301,18 +701,18 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="3" width="18.5" customWidth="1"/>
     <col min="4" max="4" width="21.625" customWidth="1"/>
-    <col min="5" max="5" width="38.6964285714286" customWidth="1"/>
+    <col min="5" max="5" width="123.625" customWidth="1"/>
     <col min="6" max="6" width="21.625" customWidth="1"/>
     <col min="7" max="7" width="13.5" customWidth="1"/>
     <col min="14" max="14" width="11.875" customWidth="1"/>
@@ -1321,7 +721,7 @@
     <col min="18" max="18" width="35.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1353,7 +753,7 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1375,7 +775,7 @@
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1407,7 +807,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -1429,7 +829,7 @@
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" ht="17.55" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
@@ -1459,7 +859,7 @@
       <c r="Q5" s="22"/>
       <c r="R5" s="5"/>
     </row>
-    <row r="6" ht="17.55" spans="2:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
         <v>17</v>
       </c>
@@ -1488,7 +888,7 @@
       <c r="Q6" s="24"/>
       <c r="R6" s="8"/>
     </row>
-    <row r="7" ht="17.55" spans="2:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B7" s="4" t="s">
         <v>20</v>
       </c>
@@ -1517,7 +917,7 @@
       <c r="Q7" s="24"/>
       <c r="R7" s="8"/>
     </row>
-    <row r="8" ht="17.55" spans="2:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
         <v>22</v>
       </c>
@@ -1546,7 +946,7 @@
       <c r="Q8" s="24"/>
       <c r="R8" s="8"/>
     </row>
-    <row r="9" ht="17.55" spans="2:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B9" s="4" t="s">
         <v>24</v>
       </c>
@@ -1575,7 +975,7 @@
       <c r="Q9" s="24"/>
       <c r="R9" s="8"/>
     </row>
-    <row r="10" ht="17.55" spans="2:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B10" s="4" t="s">
         <v>26</v>
       </c>
@@ -1604,7 +1004,7 @@
       <c r="Q10" s="24"/>
       <c r="R10" s="8"/>
     </row>
-    <row r="11" ht="17.55" spans="2:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B11" s="6" t="s">
         <v>28</v>
       </c>
@@ -1633,7 +1033,7 @@
       <c r="Q11" s="24"/>
       <c r="R11" s="8"/>
     </row>
-    <row r="12" ht="17.55" spans="2:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
@@ -1643,8 +1043,8 @@
       <c r="D12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="14" t="s">
-        <v>31</v>
+      <c r="E12" s="25" t="s">
+        <v>38</v>
       </c>
       <c r="F12" s="8">
         <v>1</v>
@@ -1662,18 +1062,18 @@
       <c r="Q12" s="24"/>
       <c r="R12" s="8"/>
     </row>
-    <row r="13" ht="17.55" spans="2:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B13" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F13" s="8">
         <v>1</v>
@@ -1691,18 +1091,18 @@
       <c r="Q13" s="24"/>
       <c r="R13" s="8"/>
     </row>
-    <row r="14" ht="17.55" spans="2:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F14" s="8">
         <v>1</v>
@@ -1720,18 +1120,18 @@
       <c r="Q14" s="24"/>
       <c r="R14" s="8"/>
     </row>
-    <row r="15" ht="17.55" spans="2:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B15" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F15" s="8">
         <v>1</v>
@@ -1749,7 +1149,7 @@
       <c r="Q15" s="24"/>
       <c r="R15" s="8"/>
     </row>
-    <row r="16" ht="17.55" spans="2:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B16" s="8"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -1768,7 +1168,7 @@
       <c r="Q16" s="24"/>
       <c r="R16" s="8"/>
     </row>
-    <row r="17" ht="17.55" spans="2:18">
+    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B17" s="8"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
@@ -1787,22 +1187,22 @@
       <c r="Q17" s="24"/>
       <c r="R17" s="8"/>
     </row>
-    <row r="18" ht="17.55" spans="2:4">
+    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B18" s="9"/>
       <c r="C18" s="10"/>
       <c r="D18" s="5"/>
     </row>
-    <row r="19" ht="17.55" spans="2:4">
+    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B19" s="9"/>
       <c r="C19" s="10"/>
       <c r="D19" s="5"/>
     </row>
-    <row r="20" ht="17.55" spans="2:3">
+    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B20" s="9"/>
       <c r="C20" s="11"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>